--- a/game44/web.xlsx
+++ b/game44/web.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>domain</t>
   </si>
@@ -45,31 +45,34 @@
     <t>play.xvlgame.top</t>
   </si>
   <si>
-    <t>#4b0082</t>
+    <t>#1660ab</t>
   </si>
   <si>
     <t>sec.ewlgame.top</t>
   </si>
   <si>
-    <t>#ba55d3</t>
+    <t>#2b313f</t>
   </si>
   <si>
     <t>sec.eqwgame.top</t>
   </si>
   <si>
-    <t>#98fb98</t>
+    <t>#ee3f4d</t>
   </si>
   <si>
     <t>sec.nigame.top</t>
   </si>
   <si>
-    <t>#c2849f</t>
+    <t>#1781b5</t>
   </si>
   <si>
     <t>sec.fxgame.top</t>
   </si>
   <si>
-    <t>#746097</t>
+    <t>#6f94cd</t>
+  </si>
+  <si>
+    <t>#0c567d</t>
   </si>
   <si>
     <t>invicts.site</t>
@@ -416,7 +419,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="61">
+  <fills count="62">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -563,31 +566,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4B0082"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA55D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98FB98"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2849F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF746097"/>
+        <fgColor rgb="FF1660AB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B313F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE3F4D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1781B5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6F94CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0C567D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -923,7 +932,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -947,16 +956,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -965,89 +974,89 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1133,17 +1142,20 @@
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1529,8 +1541,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="23.25" customWidth="1"/>
   </cols>
@@ -1585,8 +1597,18 @@
       <c r="A6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="33" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="34" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1621,18 +1643,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1667,18 +1689,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1709,61 +1731,61 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="20"/>
       <c r="I6" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:10">
@@ -1773,10 +1795,10 @@
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="I7" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1786,10 +1808,10 @@
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="I8" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1799,10 +1821,10 @@
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="I9" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1856,57 +1878,57 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
